--- a/ASTquizApp/qBanks/OMS.xlsx
+++ b/ASTquizApp/qBanks/OMS.xlsx
@@ -1,15 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26626"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\programDo\vs\ASTquizApp\ASTquizApp\qBanks\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1673E25C-ED57-4E71-A2AE-83F76EBA1E43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$36</definedName>
@@ -19,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="145" count="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="145">
   <si>
     <t>Introduction</t>
   </si>
@@ -459,50 +463,46 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="0" formatCode="General"/>
-    <numFmt numFmtId="9" formatCode="0%"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="8">
     <font>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <sz val="11"/>
     </font>
     <font>
-      <name val="Arial"/>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b/>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
+      <sz val="12"/>
       <name val="Arial"/>
-      <sz val="12"/>
     </font>
     <font>
-      <name val="Arial"/>
       <sz val="12"/>
       <color indexed="8"/>
+      <name val="Arial"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <name val="Arial"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
-      <name val="Arial"/>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="3">
@@ -564,9 +564,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -586,7 +584,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -595,20 +593,18 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -619,7 +615,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -628,14 +624,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -649,23 +643,23 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="bottom" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -679,14 +673,22 @@
       </fill>
     </dxf>
   </dxfs>
-  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16" count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -724,7 +726,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -758,6 +760,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -792,9 +795,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -900,7 +904,7 @@
             <a:camera prst="orthographicFront">
               <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
+            <a:lightRig rig="threePt" dir="t">
               <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
@@ -967,28 +971,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:T192"/>
-  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:S192"/>
+  <sheetFormatPr defaultColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" hidden="1" customWidth="1" width="20.0" style="0"/>
-    <col min="2" max="2" hidden="1" customWidth="1" bestFit="1" width="34.42578" style="0"/>
-    <col min="3" max="3" hidden="1" customWidth="1" width="10.140625" style="0"/>
-    <col min="4" max="4" hidden="1" customWidth="1" width="13.140625" style="0"/>
-    <col min="5" max="5" hidden="1" customWidth="1" bestFit="1" width="10.0" style="0"/>
-    <col min="6" max="6" hidden="1" customWidth="1" bestFit="1" width="10.0" style="0"/>
-    <col min="7" max="7" customWidth="1" bestFit="1" width="10.0" style="0"/>
-    <col min="8" max="8" customWidth="1" width="92.140625" style="0"/>
-    <col min="9" max="9" customWidth="1" width="22.855469" style="0"/>
-    <col min="10" max="10" customWidth="1" bestFit="1" width="37.710938" style="0"/>
-    <col min="11" max="11" customWidth="1" bestFit="1" width="19.0" style="0"/>
-    <col min="12" max="12" customWidth="1" bestFit="1" width="24.0" style="0"/>
-    <col min="13" max="13" customWidth="1" width="10.140625" style="0"/>
-    <col min="14" max="14" hidden="1" customWidth="1" bestFit="1" width="10.0" style="0"/>
-    <col min="15" max="15" hidden="1" customWidth="1" bestFit="1" width="10.0" style="0"/>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="92.140625" customWidth="1"/>
+    <col min="9" max="9" width="22.85546875" customWidth="1"/>
+    <col min="10" max="10" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.140625" customWidth="1"/>
+    <col min="14" max="15" width="10" hidden="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="8:8" s="1" ht="47.25" customFormat="1">
+    <row r="1" spans="1:19" s="1" customFormat="1" ht="31.5">
       <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
@@ -1039,7 +1042,7 @@
       <c r="R1" s="3"/>
       <c r="S1" s="3"/>
     </row>
-    <row r="2" spans="8:8" s="1" ht="60.0" customFormat="1">
+    <row r="2" spans="1:19" s="1" customFormat="1" ht="60">
       <c r="A2" s="4" t="s">
         <v>101</v>
       </c>
@@ -1047,7 +1050,7 @@
         <v>22</v>
       </c>
       <c r="C2" s="6">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>0</v>
@@ -1056,7 +1059,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>2</v>
@@ -1080,7 +1083,7 @@
         <v>20</v>
       </c>
       <c r="N2" s="12">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O2" s="13" t="s">
         <v>28</v>
@@ -1090,7 +1093,7 @@
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
     </row>
-    <row r="3" spans="8:8" s="1" ht="60.0" customFormat="1">
+    <row r="3" spans="1:19" s="1" customFormat="1" ht="60">
       <c r="A3" s="4" t="s">
         <v>101</v>
       </c>
@@ -1098,7 +1101,7 @@
         <v>22</v>
       </c>
       <c r="C3" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>0</v>
@@ -1107,7 +1110,7 @@
         <v>20</v>
       </c>
       <c r="F3" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>29</v>
@@ -1127,7 +1130,7 @@
         <v>19</v>
       </c>
       <c r="N3" s="12">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O3" s="13" t="s">
         <v>31</v>
@@ -1137,7 +1140,7 @@
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
     </row>
-    <row r="4" spans="8:8" s="1" ht="60.0" customFormat="1">
+    <row r="4" spans="1:19" s="1" customFormat="1" ht="60">
       <c r="A4" s="4" t="s">
         <v>101</v>
       </c>
@@ -1145,7 +1148,7 @@
         <v>22</v>
       </c>
       <c r="C4" s="6">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>32</v>
@@ -1154,7 +1157,7 @@
         <v>20</v>
       </c>
       <c r="F4" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>2</v>
@@ -1178,7 +1181,7 @@
         <v>19</v>
       </c>
       <c r="N4" s="12">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O4" s="13" t="s">
         <v>31</v>
@@ -1188,7 +1191,7 @@
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
     </row>
-    <row r="5" spans="8:8" s="1" ht="60.0" customFormat="1">
+    <row r="5" spans="1:19" s="1" customFormat="1" ht="60">
       <c r="A5" s="4" t="s">
         <v>101</v>
       </c>
@@ -1196,7 +1199,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="6">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>38</v>
@@ -1205,7 +1208,7 @@
         <v>19</v>
       </c>
       <c r="F5" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>2</v>
@@ -1229,7 +1232,7 @@
         <v>1</v>
       </c>
       <c r="N5" s="12">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O5" s="16" t="s">
         <v>31</v>
@@ -1239,7 +1242,7 @@
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
     </row>
-    <row r="6" spans="8:8" s="1" ht="60.0" customFormat="1">
+    <row r="6" spans="1:19" s="1" customFormat="1" ht="60">
       <c r="A6" s="4" t="s">
         <v>101</v>
       </c>
@@ -1247,7 +1250,7 @@
         <v>22</v>
       </c>
       <c r="C6" s="6">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>44</v>
@@ -1256,7 +1259,7 @@
         <v>21</v>
       </c>
       <c r="F6" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>29</v>
@@ -1276,7 +1279,7 @@
         <v>19</v>
       </c>
       <c r="N6" s="17">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O6" s="16" t="s">
         <v>31</v>
@@ -1286,7 +1289,7 @@
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
     </row>
-    <row r="7" spans="8:8" s="1" ht="60.0" customFormat="1">
+    <row r="7" spans="1:19" s="1" customFormat="1" ht="60">
       <c r="A7" s="4" t="s">
         <v>101</v>
       </c>
@@ -1294,7 +1297,7 @@
         <v>22</v>
       </c>
       <c r="C7" s="6">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>46</v>
@@ -1303,7 +1306,7 @@
         <v>20</v>
       </c>
       <c r="F7" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>2</v>
@@ -1327,7 +1330,7 @@
         <v>19</v>
       </c>
       <c r="N7" s="17">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O7" s="16" t="s">
         <v>3</v>
@@ -1337,7 +1340,7 @@
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
     </row>
-    <row r="8" spans="8:8" s="1" ht="75.0" customFormat="1">
+    <row r="8" spans="1:19" s="1" customFormat="1" ht="75">
       <c r="A8" s="4" t="s">
         <v>101</v>
       </c>
@@ -1345,7 +1348,7 @@
         <v>22</v>
       </c>
       <c r="C8" s="6">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>46</v>
@@ -1354,7 +1357,7 @@
         <v>21</v>
       </c>
       <c r="F8" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>2</v>
@@ -1378,7 +1381,7 @@
         <v>21</v>
       </c>
       <c r="N8" s="17">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O8" s="16" t="s">
         <v>3</v>
@@ -1388,7 +1391,7 @@
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
     </row>
-    <row r="9" spans="8:8" ht="60.0">
+    <row r="9" spans="1:19" ht="60">
       <c r="A9" s="4" t="s">
         <v>101</v>
       </c>
@@ -1396,7 +1399,7 @@
         <v>22</v>
       </c>
       <c r="C9" s="6">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>0</v>
@@ -1405,7 +1408,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>2</v>
@@ -1429,7 +1432,7 @@
         <v>19</v>
       </c>
       <c r="N9" s="17">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O9" s="16" t="s">
         <v>31</v>
@@ -1439,7 +1442,7 @@
       <c r="R9" s="19"/>
       <c r="S9" s="19"/>
     </row>
-    <row r="10" spans="8:8" ht="60.0">
+    <row r="10" spans="1:19" ht="60">
       <c r="A10" s="4" t="s">
         <v>101</v>
       </c>
@@ -1447,7 +1450,7 @@
         <v>22</v>
       </c>
       <c r="C10" s="6">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="D10" s="14" t="s">
         <v>0</v>
@@ -1456,7 +1459,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G10" s="20" t="s">
         <v>2</v>
@@ -1480,7 +1483,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="23">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O10" s="20" t="s">
         <v>31</v>
@@ -1490,7 +1493,7 @@
       <c r="R10" s="19"/>
       <c r="S10" s="19"/>
     </row>
-    <row r="11" spans="8:8" ht="60.0">
+    <row r="11" spans="1:19" ht="60">
       <c r="A11" s="4" t="s">
         <v>101</v>
       </c>
@@ -1498,7 +1501,7 @@
         <v>22</v>
       </c>
       <c r="C11" s="6">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="D11" s="14" t="s">
         <v>0</v>
@@ -1507,7 +1510,7 @@
         <v>19</v>
       </c>
       <c r="F11" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G11" s="20" t="s">
         <v>29</v>
@@ -1527,7 +1530,7 @@
         <v>1</v>
       </c>
       <c r="N11" s="23">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O11" s="20" t="s">
         <v>31</v>
@@ -1537,7 +1540,7 @@
       <c r="R11" s="19"/>
       <c r="S11" s="19"/>
     </row>
-    <row r="12" spans="8:8" ht="60.0">
+    <row r="12" spans="1:19" ht="60">
       <c r="A12" s="4" t="s">
         <v>101</v>
       </c>
@@ -1545,7 +1548,7 @@
         <v>22</v>
       </c>
       <c r="C12" s="6">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>46</v>
@@ -1554,7 +1557,7 @@
         <v>19</v>
       </c>
       <c r="F12" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G12" s="20" t="s">
         <v>2</v>
@@ -1578,7 +1581,7 @@
         <v>21</v>
       </c>
       <c r="N12" s="23">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O12" s="20" t="s">
         <v>3</v>
@@ -1588,7 +1591,7 @@
       <c r="R12" s="19"/>
       <c r="S12" s="19"/>
     </row>
-    <row r="13" spans="8:8" ht="60.0">
+    <row r="13" spans="1:19" ht="60">
       <c r="A13" s="4" t="s">
         <v>101</v>
       </c>
@@ -1596,7 +1599,7 @@
         <v>22</v>
       </c>
       <c r="C13" s="6">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="D13" s="14" t="s">
         <v>46</v>
@@ -1605,7 +1608,7 @@
         <v>19</v>
       </c>
       <c r="F13" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G13" s="20" t="s">
         <v>29</v>
@@ -1625,7 +1628,7 @@
         <v>19</v>
       </c>
       <c r="N13" s="23">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O13" s="20" t="s">
         <v>3</v>
@@ -1635,7 +1638,7 @@
       <c r="R13" s="19"/>
       <c r="S13" s="19"/>
     </row>
-    <row r="14" spans="8:8" ht="75.0">
+    <row r="14" spans="1:19" ht="75">
       <c r="A14" s="4" t="s">
         <v>101</v>
       </c>
@@ -1643,7 +1646,7 @@
         <v>22</v>
       </c>
       <c r="C14" s="6">
-        <v>13.0</v>
+        <v>13</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>46</v>
@@ -1652,7 +1655,7 @@
         <v>19</v>
       </c>
       <c r="F14" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G14" s="20" t="s">
         <v>2</v>
@@ -1676,7 +1679,7 @@
         <v>20</v>
       </c>
       <c r="N14" s="23">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O14" s="20" t="s">
         <v>3</v>
@@ -1686,7 +1689,7 @@
       <c r="R14" s="19"/>
       <c r="S14" s="19"/>
     </row>
-    <row r="15" spans="8:8" ht="90.0">
+    <row r="15" spans="1:19" ht="90">
       <c r="A15" s="4" t="s">
         <v>101</v>
       </c>
@@ -1694,7 +1697,7 @@
         <v>22</v>
       </c>
       <c r="C15" s="6">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>46</v>
@@ -1703,7 +1706,7 @@
         <v>20</v>
       </c>
       <c r="F15" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G15" s="20" t="s">
         <v>2</v>
@@ -1727,7 +1730,7 @@
         <v>20</v>
       </c>
       <c r="N15" s="23">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O15" s="20" t="s">
         <v>3</v>
@@ -1737,7 +1740,7 @@
       <c r="R15" s="19"/>
       <c r="S15" s="19"/>
     </row>
-    <row r="16" spans="8:8" ht="60.0">
+    <row r="16" spans="1:19" ht="60">
       <c r="A16" s="4" t="s">
         <v>101</v>
       </c>
@@ -1745,7 +1748,7 @@
         <v>22</v>
       </c>
       <c r="C16" s="6">
-        <v>15.0</v>
+        <v>15</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>46</v>
@@ -1754,7 +1757,7 @@
         <v>21</v>
       </c>
       <c r="F16" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G16" s="20" t="s">
         <v>2</v>
@@ -1778,7 +1781,7 @@
         <v>19</v>
       </c>
       <c r="N16" s="23">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O16" s="20" t="s">
         <v>3</v>
@@ -1788,7 +1791,7 @@
       <c r="R16" s="19"/>
       <c r="S16" s="19"/>
     </row>
-    <row r="17" spans="8:8" ht="60.0">
+    <row r="17" spans="1:19" ht="60">
       <c r="A17" s="4" t="s">
         <v>101</v>
       </c>
@@ -1796,7 +1799,7 @@
         <v>22</v>
       </c>
       <c r="C17" s="6">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="D17" s="14" t="s">
         <v>38</v>
@@ -1805,7 +1808,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G17" s="20" t="s">
         <v>2</v>
@@ -1829,7 +1832,7 @@
         <v>21</v>
       </c>
       <c r="N17" s="23">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O17" s="20" t="s">
         <v>31</v>
@@ -1839,7 +1842,7 @@
       <c r="R17" s="19"/>
       <c r="S17" s="19"/>
     </row>
-    <row r="18" spans="8:8" ht="60.0">
+    <row r="18" spans="1:19" ht="60">
       <c r="A18" s="4" t="s">
         <v>101</v>
       </c>
@@ -1847,7 +1850,7 @@
         <v>22</v>
       </c>
       <c r="C18" s="6">
-        <v>17.0</v>
+        <v>17</v>
       </c>
       <c r="D18" s="14" t="s">
         <v>46</v>
@@ -1856,7 +1859,7 @@
         <v>21</v>
       </c>
       <c r="F18" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G18" s="20" t="s">
         <v>29</v>
@@ -1876,7 +1879,7 @@
         <v>1</v>
       </c>
       <c r="N18" s="23">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O18" s="20" t="s">
         <v>3</v>
@@ -1886,7 +1889,7 @@
       <c r="R18" s="19"/>
       <c r="S18" s="19"/>
     </row>
-    <row r="19" spans="8:8" ht="60.0">
+    <row r="19" spans="1:19" ht="60">
       <c r="A19" s="4" t="s">
         <v>101</v>
       </c>
@@ -1894,7 +1897,7 @@
         <v>22</v>
       </c>
       <c r="C19" s="6">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="D19" s="14" t="s">
         <v>46</v>
@@ -1903,7 +1906,7 @@
         <v>21</v>
       </c>
       <c r="F19" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>29</v>
@@ -1923,7 +1926,7 @@
         <v>19</v>
       </c>
       <c r="N19" s="23">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O19" s="20" t="s">
         <v>3</v>
@@ -1933,7 +1936,7 @@
       <c r="R19" s="19"/>
       <c r="S19" s="19"/>
     </row>
-    <row r="20" spans="8:8" ht="60.0">
+    <row r="20" spans="1:19" ht="60">
       <c r="A20" s="4" t="s">
         <v>101</v>
       </c>
@@ -1941,7 +1944,7 @@
         <v>22</v>
       </c>
       <c r="C20" s="6">
-        <v>19.0</v>
+        <v>19</v>
       </c>
       <c r="D20" s="14" t="s">
         <v>46</v>
@@ -1950,7 +1953,7 @@
         <v>20</v>
       </c>
       <c r="F20" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G20" s="20" t="s">
         <v>29</v>
@@ -1970,7 +1973,7 @@
         <v>19</v>
       </c>
       <c r="N20" s="23">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O20" s="20" t="s">
         <v>3</v>
@@ -1980,7 +1983,7 @@
       <c r="R20" s="19"/>
       <c r="S20" s="19"/>
     </row>
-    <row r="21" spans="8:8" ht="60.0">
+    <row r="21" spans="1:19" ht="60">
       <c r="A21" s="4" t="s">
         <v>101</v>
       </c>
@@ -1988,7 +1991,7 @@
         <v>22</v>
       </c>
       <c r="C21" s="6">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="D21" s="14" t="s">
         <v>90</v>
@@ -1997,7 +2000,7 @@
         <v>1</v>
       </c>
       <c r="F21" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G21" s="20" t="s">
         <v>2</v>
@@ -2021,7 +2024,7 @@
         <v>20</v>
       </c>
       <c r="N21" s="23">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O21" s="20" t="s">
         <v>3</v>
@@ -2031,7 +2034,7 @@
       <c r="R21" s="19"/>
       <c r="S21" s="19"/>
     </row>
-    <row r="22" spans="8:8" ht="60.0">
+    <row r="22" spans="1:19" ht="60">
       <c r="A22" s="4" t="s">
         <v>101</v>
       </c>
@@ -2039,7 +2042,7 @@
         <v>22</v>
       </c>
       <c r="C22" s="6">
-        <v>21.0</v>
+        <v>21</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>90</v>
@@ -2048,7 +2051,7 @@
         <v>1</v>
       </c>
       <c r="F22" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G22" s="20" t="s">
         <v>29</v>
@@ -2068,7 +2071,7 @@
         <v>19</v>
       </c>
       <c r="N22" s="23">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O22" s="20" t="s">
         <v>3</v>
@@ -2078,7 +2081,7 @@
       <c r="R22" s="19"/>
       <c r="S22" s="19"/>
     </row>
-    <row r="23" spans="8:8" ht="60.0">
+    <row r="23" spans="1:19" ht="60">
       <c r="A23" s="4" t="s">
         <v>101</v>
       </c>
@@ -2086,7 +2089,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="6">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="D23" s="14" t="s">
         <v>44</v>
@@ -2095,7 +2098,7 @@
         <v>20</v>
       </c>
       <c r="F23" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G23" s="20" t="s">
         <v>29</v>
@@ -2115,7 +2118,7 @@
         <v>19</v>
       </c>
       <c r="N23" s="23">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O23" s="20" t="s">
         <v>3</v>
@@ -2125,7 +2128,7 @@
       <c r="R23" s="19"/>
       <c r="S23" s="19"/>
     </row>
-    <row r="24" spans="8:8" ht="60.0">
+    <row r="24" spans="1:19" ht="60">
       <c r="A24" s="4" t="s">
         <v>101</v>
       </c>
@@ -2133,7 +2136,7 @@
         <v>22</v>
       </c>
       <c r="C24" s="6">
-        <v>23.0</v>
+        <v>23</v>
       </c>
       <c r="D24" s="14" t="s">
         <v>44</v>
@@ -2142,7 +2145,7 @@
         <v>21</v>
       </c>
       <c r="F24" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G24" s="20" t="s">
         <v>29</v>
@@ -2162,7 +2165,7 @@
         <v>19</v>
       </c>
       <c r="N24" s="23">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O24" s="20" t="s">
         <v>3</v>
@@ -2172,7 +2175,7 @@
       <c r="R24" s="19"/>
       <c r="S24" s="19"/>
     </row>
-    <row r="25" spans="8:8" ht="60.0">
+    <row r="25" spans="1:19" ht="60">
       <c r="A25" s="4" t="s">
         <v>101</v>
       </c>
@@ -2180,7 +2183,7 @@
         <v>22</v>
       </c>
       <c r="C25" s="6">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="D25" s="14" t="s">
         <v>38</v>
@@ -2189,7 +2192,7 @@
         <v>20</v>
       </c>
       <c r="F25" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G25" s="20" t="s">
         <v>29</v>
@@ -2209,7 +2212,7 @@
         <v>1</v>
       </c>
       <c r="N25" s="23">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O25" s="20" t="s">
         <v>3</v>
@@ -2219,7 +2222,7 @@
       <c r="R25" s="19"/>
       <c r="S25" s="19"/>
     </row>
-    <row r="26" spans="8:8" ht="60.0">
+    <row r="26" spans="1:19" ht="60">
       <c r="A26" s="4" t="s">
         <v>101</v>
       </c>
@@ -2227,7 +2230,7 @@
         <v>22</v>
       </c>
       <c r="C26" s="6">
-        <v>25.0</v>
+        <v>25</v>
       </c>
       <c r="D26" s="14" t="s">
         <v>38</v>
@@ -2236,7 +2239,7 @@
         <v>21</v>
       </c>
       <c r="F26" s="8">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G26" s="20" t="s">
         <v>29</v>
@@ -2256,7 +2259,7 @@
         <v>19</v>
       </c>
       <c r="N26" s="23">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="O26" s="20" t="s">
         <v>3</v>
@@ -2266,7 +2269,7 @@
       <c r="R26" s="19"/>
       <c r="S26" s="19"/>
     </row>
-    <row r="27" spans="8:8" s="28" ht="60.0" customFormat="1">
+    <row r="27" spans="1:19" s="28" customFormat="1" ht="60">
       <c r="A27" s="4" t="s">
         <v>101</v>
       </c>
@@ -2274,7 +2277,7 @@
         <v>22</v>
       </c>
       <c r="C27" s="6">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="D27" s="29" t="s">
         <v>102</v>
@@ -2283,7 +2286,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="29">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G27" s="29" t="s">
         <v>2</v>
@@ -2307,13 +2310,13 @@
         <v>21</v>
       </c>
       <c r="N27" s="29">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O27" s="29" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="28" spans="8:8" s="28" ht="60.0" customFormat="1">
+    <row r="28" spans="1:19" s="28" customFormat="1" ht="60">
       <c r="A28" s="4" t="s">
         <v>101</v>
       </c>
@@ -2321,7 +2324,7 @@
         <v>22</v>
       </c>
       <c r="C28" s="6">
-        <v>27.0</v>
+        <v>27</v>
       </c>
       <c r="D28" s="29" t="s">
         <v>102</v>
@@ -2330,7 +2333,7 @@
         <v>20</v>
       </c>
       <c r="F28" s="29">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G28" s="29" t="s">
         <v>2</v>
@@ -2339,7 +2342,7 @@
         <v>109</v>
       </c>
       <c r="I28" s="31">
-        <v>0.55</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="J28" s="31">
         <v>0.75</v>
@@ -2354,13 +2357,13 @@
         <v>19</v>
       </c>
       <c r="N28" s="29">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O28" s="29" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="29" spans="8:8" s="28" ht="60.0" customFormat="1">
+    <row r="29" spans="1:19" s="28" customFormat="1" ht="60">
       <c r="A29" s="4" t="s">
         <v>101</v>
       </c>
@@ -2368,7 +2371,7 @@
         <v>22</v>
       </c>
       <c r="C29" s="6">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="D29" s="29" t="s">
         <v>102</v>
@@ -2377,7 +2380,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="29">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G29" s="29" t="s">
         <v>2</v>
@@ -2401,13 +2404,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="29">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O29" s="29" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="30" spans="8:8" s="28" ht="60.0" customFormat="1">
+    <row r="30" spans="1:19" s="28" customFormat="1" ht="60">
       <c r="A30" s="4" t="s">
         <v>101</v>
       </c>
@@ -2415,7 +2418,7 @@
         <v>22</v>
       </c>
       <c r="C30" s="6">
-        <v>29.0</v>
+        <v>29</v>
       </c>
       <c r="D30" s="29" t="s">
         <v>102</v>
@@ -2424,7 +2427,7 @@
         <v>20</v>
       </c>
       <c r="F30" s="29">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G30" s="29" t="s">
         <v>2</v>
@@ -2448,13 +2451,13 @@
         <v>20</v>
       </c>
       <c r="N30" s="29">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O30" s="29" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="31" spans="8:8" s="28" ht="60.0" customFormat="1">
+    <row r="31" spans="1:19" s="28" customFormat="1" ht="60">
       <c r="A31" s="4" t="s">
         <v>101</v>
       </c>
@@ -2462,7 +2465,7 @@
         <v>22</v>
       </c>
       <c r="C31" s="6">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="D31" s="29" t="s">
         <v>102</v>
@@ -2471,7 +2474,7 @@
         <v>19</v>
       </c>
       <c r="F31" s="29">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G31" s="29" t="s">
         <v>2</v>
@@ -2495,13 +2498,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="29">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O31" s="29" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="32" spans="8:8" s="28" ht="60.0" customFormat="1">
+    <row r="32" spans="1:19" s="28" customFormat="1" ht="60">
       <c r="A32" s="4" t="s">
         <v>101</v>
       </c>
@@ -2509,7 +2512,7 @@
         <v>22</v>
       </c>
       <c r="C32" s="6">
-        <v>31.0</v>
+        <v>31</v>
       </c>
       <c r="D32" s="29" t="s">
         <v>125</v>
@@ -2518,7 +2521,7 @@
         <v>21</v>
       </c>
       <c r="F32" s="29">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G32" s="29" t="s">
         <v>2</v>
@@ -2542,13 +2545,13 @@
         <v>20</v>
       </c>
       <c r="N32" s="29">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O32" s="29" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="33" spans="8:8" s="28" ht="60.0" customFormat="1">
+    <row r="33" spans="1:19" s="28" customFormat="1" ht="60">
       <c r="A33" s="4" t="s">
         <v>101</v>
       </c>
@@ -2556,7 +2559,7 @@
         <v>22</v>
       </c>
       <c r="C33" s="6">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="D33" s="29" t="s">
         <v>125</v>
@@ -2565,7 +2568,7 @@
         <v>19</v>
       </c>
       <c r="F33" s="29">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G33" s="29" t="s">
         <v>2</v>
@@ -2589,13 +2592,13 @@
         <v>21</v>
       </c>
       <c r="N33" s="29">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O33" s="29" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="34" spans="8:8" s="28" ht="60.0" customFormat="1">
+    <row r="34" spans="1:19" s="28" customFormat="1" ht="60">
       <c r="A34" s="4" t="s">
         <v>101</v>
       </c>
@@ -2603,7 +2606,7 @@
         <v>22</v>
       </c>
       <c r="C34" s="6">
-        <v>33.0</v>
+        <v>33</v>
       </c>
       <c r="D34" s="29" t="s">
         <v>135</v>
@@ -2612,7 +2615,7 @@
         <v>20</v>
       </c>
       <c r="F34" s="29">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G34" s="29" t="s">
         <v>2</v>
@@ -2636,13 +2639,13 @@
         <v>19</v>
       </c>
       <c r="N34" s="29">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O34" s="29" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="35" spans="8:8" s="28" ht="60.0" customFormat="1">
+    <row r="35" spans="1:19" s="28" customFormat="1" ht="60">
       <c r="A35" s="4" t="s">
         <v>101</v>
       </c>
@@ -2650,7 +2653,7 @@
         <v>22</v>
       </c>
       <c r="C35" s="6">
-        <v>34.0</v>
+        <v>34</v>
       </c>
       <c r="D35" s="29" t="s">
         <v>135</v>
@@ -2659,7 +2662,7 @@
         <v>21</v>
       </c>
       <c r="F35" s="29">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G35" s="29" t="s">
         <v>2</v>
@@ -2683,13 +2686,13 @@
         <v>19</v>
       </c>
       <c r="N35" s="29">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O35" s="29" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="36" spans="8:8" s="28" ht="60.0" customFormat="1">
+    <row r="36" spans="1:19" s="28" customFormat="1" ht="60">
       <c r="A36" s="4" t="s">
         <v>101</v>
       </c>
@@ -2697,7 +2700,7 @@
         <v>22</v>
       </c>
       <c r="C36" s="6">
-        <v>35.0</v>
+        <v>35</v>
       </c>
       <c r="D36" s="29" t="s">
         <v>135</v>
@@ -2706,7 +2709,7 @@
         <v>21</v>
       </c>
       <c r="F36" s="29">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G36" s="29" t="s">
         <v>2</v>
@@ -2730,13 +2733,13 @@
         <v>20</v>
       </c>
       <c r="N36" s="29">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="O36" s="29" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="37" spans="8:8" ht="15.75">
+    <row r="37" spans="1:19" ht="15.75">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="6"/>
@@ -2757,7 +2760,7 @@
       <c r="R37" s="19"/>
       <c r="S37" s="19"/>
     </row>
-    <row r="38" spans="8:8" ht="15.75">
+    <row r="38" spans="1:19" ht="15.75">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -2778,7 +2781,7 @@
       <c r="R38" s="19"/>
       <c r="S38" s="19"/>
     </row>
-    <row r="39" spans="8:8" ht="15.75">
+    <row r="39" spans="1:19" ht="15.75">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -2799,7 +2802,7 @@
       <c r="R39" s="19"/>
       <c r="S39" s="19"/>
     </row>
-    <row r="40" spans="8:8" ht="15.75">
+    <row r="40" spans="1:19" ht="15.75">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -2820,7 +2823,7 @@
       <c r="R40" s="19"/>
       <c r="S40" s="19"/>
     </row>
-    <row r="41" spans="8:8">
+    <row r="41" spans="1:19">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -2841,7 +2844,7 @@
       <c r="R41" s="19"/>
       <c r="S41" s="19"/>
     </row>
-    <row r="42" spans="8:8">
+    <row r="42" spans="1:19">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -2862,7 +2865,7 @@
       <c r="R42" s="19"/>
       <c r="S42" s="19"/>
     </row>
-    <row r="43" spans="8:8">
+    <row r="43" spans="1:19">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -2883,7 +2886,7 @@
       <c r="R43" s="19"/>
       <c r="S43" s="19"/>
     </row>
-    <row r="44" spans="8:8" s="35" ht="15.0" customFormat="1">
+    <row r="44" spans="1:19" s="35" customFormat="1">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -2904,7 +2907,7 @@
       <c r="R44" s="36"/>
       <c r="S44" s="36"/>
     </row>
-    <row r="45" spans="8:8">
+    <row r="45" spans="1:19">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -2925,7 +2928,7 @@
       <c r="R45" s="19"/>
       <c r="S45" s="19"/>
     </row>
-    <row r="46" spans="8:8">
+    <row r="46" spans="1:19">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -2946,7 +2949,7 @@
       <c r="R46" s="19"/>
       <c r="S46" s="19"/>
     </row>
-    <row r="47" spans="8:8">
+    <row r="47" spans="1:19">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -2967,7 +2970,7 @@
       <c r="R47" s="19"/>
       <c r="S47" s="19"/>
     </row>
-    <row r="48" spans="8:8">
+    <row r="48" spans="1:19">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -2988,7 +2991,7 @@
       <c r="R48" s="19"/>
       <c r="S48" s="19"/>
     </row>
-    <row r="49" spans="8:8">
+    <row r="49" spans="1:19">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -3009,7 +3012,7 @@
       <c r="R49" s="19"/>
       <c r="S49" s="19"/>
     </row>
-    <row r="50" spans="8:8">
+    <row r="50" spans="1:19">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -3030,7 +3033,7 @@
       <c r="R50" s="19"/>
       <c r="S50" s="19"/>
     </row>
-    <row r="51" spans="8:8">
+    <row r="51" spans="1:19">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -3051,7 +3054,7 @@
       <c r="R51" s="19"/>
       <c r="S51" s="19"/>
     </row>
-    <row r="52" spans="8:8">
+    <row r="52" spans="1:19">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -3072,7 +3075,7 @@
       <c r="R52" s="19"/>
       <c r="S52" s="19"/>
     </row>
-    <row r="53" spans="8:8" ht="15.75">
+    <row r="53" spans="1:19" ht="15.75">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -3093,7 +3096,7 @@
       <c r="R53" s="19"/>
       <c r="S53" s="19"/>
     </row>
-    <row r="54" spans="8:8" ht="15.75">
+    <row r="54" spans="1:19" ht="15.75">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -3114,7 +3117,7 @@
       <c r="R54" s="19"/>
       <c r="S54" s="19"/>
     </row>
-    <row r="55" spans="8:8" ht="15.75">
+    <row r="55" spans="1:19" ht="15.75">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -3135,7 +3138,7 @@
       <c r="R55" s="19"/>
       <c r="S55" s="19"/>
     </row>
-    <row r="56" spans="8:8" ht="15.75">
+    <row r="56" spans="1:19" ht="15.75">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -3156,7 +3159,7 @@
       <c r="R56" s="19"/>
       <c r="S56" s="19"/>
     </row>
-    <row r="57" spans="8:8">
+    <row r="57" spans="1:19">
       <c r="A57" s="19"/>
       <c r="B57" s="19"/>
       <c r="C57" s="19"/>
@@ -3177,7 +3180,7 @@
       <c r="R57" s="19"/>
       <c r="S57" s="19"/>
     </row>
-    <row r="58" spans="8:8">
+    <row r="58" spans="1:19">
       <c r="A58" s="19"/>
       <c r="B58" s="19"/>
       <c r="C58" s="19"/>
@@ -3198,7 +3201,7 @@
       <c r="R58" s="19"/>
       <c r="S58" s="19"/>
     </row>
-    <row r="59" spans="8:8">
+    <row r="59" spans="1:19">
       <c r="A59" s="19"/>
       <c r="B59" s="19"/>
       <c r="C59" s="19"/>
@@ -3219,7 +3222,7 @@
       <c r="R59" s="19"/>
       <c r="S59" s="19"/>
     </row>
-    <row r="60" spans="8:8">
+    <row r="60" spans="1:19">
       <c r="A60" s="19"/>
       <c r="B60" s="19"/>
       <c r="C60" s="19"/>
@@ -3240,7 +3243,7 @@
       <c r="R60" s="19"/>
       <c r="S60" s="19"/>
     </row>
-    <row r="61" spans="8:8">
+    <row r="61" spans="1:19">
       <c r="A61" s="19"/>
       <c r="B61" s="19"/>
       <c r="C61" s="19"/>
@@ -3261,7 +3264,7 @@
       <c r="R61" s="19"/>
       <c r="S61" s="19"/>
     </row>
-    <row r="62" spans="8:8">
+    <row r="62" spans="1:19">
       <c r="A62" s="19"/>
       <c r="B62" s="19"/>
       <c r="C62" s="19"/>
@@ -3282,7 +3285,7 @@
       <c r="R62" s="19"/>
       <c r="S62" s="19"/>
     </row>
-    <row r="63" spans="8:8">
+    <row r="63" spans="1:19">
       <c r="A63" s="19"/>
       <c r="B63" s="19"/>
       <c r="C63" s="19"/>
@@ -3303,7 +3306,7 @@
       <c r="R63" s="19"/>
       <c r="S63" s="19"/>
     </row>
-    <row r="64" spans="8:8">
+    <row r="64" spans="1:19">
       <c r="A64" s="19"/>
       <c r="B64" s="19"/>
       <c r="C64" s="19"/>
@@ -3324,7 +3327,7 @@
       <c r="R64" s="19"/>
       <c r="S64" s="19"/>
     </row>
-    <row r="65" spans="8:8">
+    <row r="65" spans="1:19">
       <c r="A65" s="19"/>
       <c r="B65" s="19"/>
       <c r="C65" s="19"/>
@@ -3345,7 +3348,7 @@
       <c r="R65" s="19"/>
       <c r="S65" s="19"/>
     </row>
-    <row r="66" spans="8:8">
+    <row r="66" spans="1:19">
       <c r="A66" s="19"/>
       <c r="B66" s="19"/>
       <c r="C66" s="19"/>
@@ -3366,7 +3369,7 @@
       <c r="R66" s="19"/>
       <c r="S66" s="19"/>
     </row>
-    <row r="67" spans="8:8">
+    <row r="67" spans="1:19">
       <c r="A67" s="19"/>
       <c r="B67" s="19"/>
       <c r="C67" s="19"/>
@@ -3387,7 +3390,7 @@
       <c r="R67" s="19"/>
       <c r="S67" s="19"/>
     </row>
-    <row r="68" spans="8:8">
+    <row r="68" spans="1:19">
       <c r="A68" s="19"/>
       <c r="B68" s="19"/>
       <c r="C68" s="19"/>
@@ -3408,7 +3411,7 @@
       <c r="R68" s="19"/>
       <c r="S68" s="19"/>
     </row>
-    <row r="69" spans="8:8">
+    <row r="69" spans="1:19">
       <c r="A69" s="19"/>
       <c r="B69" s="19"/>
       <c r="C69" s="19"/>
@@ -3429,7 +3432,7 @@
       <c r="R69" s="19"/>
       <c r="S69" s="19"/>
     </row>
-    <row r="70" spans="8:8">
+    <row r="70" spans="1:19">
       <c r="A70" s="19"/>
       <c r="B70" s="19"/>
       <c r="C70" s="19"/>
@@ -3450,7 +3453,7 @@
       <c r="R70" s="19"/>
       <c r="S70" s="19"/>
     </row>
-    <row r="71" spans="8:8">
+    <row r="71" spans="1:19">
       <c r="A71" s="19"/>
       <c r="B71" s="19"/>
       <c r="C71" s="19"/>
@@ -3471,7 +3474,7 @@
       <c r="R71" s="19"/>
       <c r="S71" s="19"/>
     </row>
-    <row r="72" spans="8:8">
+    <row r="72" spans="1:19">
       <c r="A72" s="19"/>
       <c r="B72" s="19"/>
       <c r="C72" s="19"/>
@@ -3492,7 +3495,7 @@
       <c r="R72" s="19"/>
       <c r="S72" s="19"/>
     </row>
-    <row r="73" spans="8:8">
+    <row r="73" spans="1:19">
       <c r="A73" s="19"/>
       <c r="B73" s="19"/>
       <c r="C73" s="19"/>
@@ -3513,7 +3516,7 @@
       <c r="R73" s="19"/>
       <c r="S73" s="19"/>
     </row>
-    <row r="74" spans="8:8">
+    <row r="74" spans="1:19">
       <c r="A74" s="19"/>
       <c r="B74" s="19"/>
       <c r="C74" s="19"/>
@@ -3534,7 +3537,7 @@
       <c r="R74" s="19"/>
       <c r="S74" s="19"/>
     </row>
-    <row r="75" spans="8:8">
+    <row r="75" spans="1:19">
       <c r="A75" s="19"/>
       <c r="B75" s="19"/>
       <c r="C75" s="19"/>
@@ -3555,7 +3558,7 @@
       <c r="R75" s="19"/>
       <c r="S75" s="19"/>
     </row>
-    <row r="76" spans="8:8">
+    <row r="76" spans="1:19">
       <c r="A76" s="19"/>
       <c r="B76" s="19"/>
       <c r="C76" s="19"/>
@@ -3576,7 +3579,7 @@
       <c r="R76" s="19"/>
       <c r="S76" s="19"/>
     </row>
-    <row r="77" spans="8:8">
+    <row r="77" spans="1:19">
       <c r="A77" s="19"/>
       <c r="B77" s="19"/>
       <c r="C77" s="19"/>
@@ -3597,7 +3600,7 @@
       <c r="R77" s="19"/>
       <c r="S77" s="19"/>
     </row>
-    <row r="78" spans="8:8">
+    <row r="78" spans="1:19">
       <c r="A78" s="19"/>
       <c r="B78" s="19"/>
       <c r="C78" s="19"/>
@@ -3618,7 +3621,7 @@
       <c r="R78" s="19"/>
       <c r="S78" s="19"/>
     </row>
-    <row r="79" spans="8:8">
+    <row r="79" spans="1:19">
       <c r="A79" s="19"/>
       <c r="B79" s="19"/>
       <c r="C79" s="19"/>
@@ -3639,7 +3642,7 @@
       <c r="R79" s="19"/>
       <c r="S79" s="19"/>
     </row>
-    <row r="80" spans="8:8">
+    <row r="80" spans="1:19">
       <c r="A80" s="19"/>
       <c r="B80" s="19"/>
       <c r="C80" s="19"/>
@@ -3660,7 +3663,7 @@
       <c r="R80" s="19"/>
       <c r="S80" s="19"/>
     </row>
-    <row r="81" spans="8:8">
+    <row r="81" spans="1:19">
       <c r="A81" s="19"/>
       <c r="B81" s="19"/>
       <c r="C81" s="19"/>
@@ -3681,7 +3684,7 @@
       <c r="R81" s="19"/>
       <c r="S81" s="19"/>
     </row>
-    <row r="82" spans="8:8">
+    <row r="82" spans="1:19">
       <c r="A82" s="19"/>
       <c r="B82" s="19"/>
       <c r="C82" s="19"/>
@@ -3702,7 +3705,7 @@
       <c r="R82" s="19"/>
       <c r="S82" s="19"/>
     </row>
-    <row r="83" spans="8:8">
+    <row r="83" spans="1:19">
       <c r="A83" s="19"/>
       <c r="B83" s="19"/>
       <c r="C83" s="19"/>
@@ -3723,7 +3726,7 @@
       <c r="R83" s="19"/>
       <c r="S83" s="19"/>
     </row>
-    <row r="84" spans="8:8">
+    <row r="84" spans="1:19">
       <c r="A84" s="19"/>
       <c r="B84" s="19"/>
       <c r="C84" s="19"/>
@@ -3744,7 +3747,7 @@
       <c r="R84" s="19"/>
       <c r="S84" s="19"/>
     </row>
-    <row r="85" spans="8:8">
+    <row r="85" spans="1:19">
       <c r="A85" s="19"/>
       <c r="B85" s="19"/>
       <c r="C85" s="19"/>
@@ -3765,7 +3768,7 @@
       <c r="R85" s="19"/>
       <c r="S85" s="19"/>
     </row>
-    <row r="86" spans="8:8">
+    <row r="86" spans="1:19">
       <c r="A86" s="19"/>
       <c r="B86" s="19"/>
       <c r="C86" s="19"/>
@@ -3786,7 +3789,7 @@
       <c r="R86" s="19"/>
       <c r="S86" s="19"/>
     </row>
-    <row r="87" spans="8:8">
+    <row r="87" spans="1:19">
       <c r="A87" s="19"/>
       <c r="B87" s="19"/>
       <c r="C87" s="19"/>
@@ -3807,7 +3810,7 @@
       <c r="R87" s="19"/>
       <c r="S87" s="19"/>
     </row>
-    <row r="88" spans="8:8">
+    <row r="88" spans="1:19">
       <c r="A88" s="19"/>
       <c r="B88" s="19"/>
       <c r="C88" s="19"/>
@@ -3828,7 +3831,7 @@
       <c r="R88" s="19"/>
       <c r="S88" s="19"/>
     </row>
-    <row r="89" spans="8:8">
+    <row r="89" spans="1:19">
       <c r="A89" s="19"/>
       <c r="B89" s="19"/>
       <c r="C89" s="19"/>
@@ -3849,7 +3852,7 @@
       <c r="R89" s="19"/>
       <c r="S89" s="19"/>
     </row>
-    <row r="90" spans="8:8">
+    <row r="90" spans="1:19">
       <c r="A90" s="19"/>
       <c r="B90" s="19"/>
       <c r="C90" s="19"/>
@@ -3870,7 +3873,7 @@
       <c r="R90" s="19"/>
       <c r="S90" s="19"/>
     </row>
-    <row r="91" spans="8:8">
+    <row r="91" spans="1:19">
       <c r="A91" s="19"/>
       <c r="B91" s="19"/>
       <c r="C91" s="19"/>
@@ -3891,7 +3894,7 @@
       <c r="R91" s="19"/>
       <c r="S91" s="19"/>
     </row>
-    <row r="92" spans="8:8">
+    <row r="92" spans="1:19">
       <c r="A92" s="19"/>
       <c r="B92" s="19"/>
       <c r="C92" s="19"/>
@@ -3912,7 +3915,7 @@
       <c r="R92" s="19"/>
       <c r="S92" s="19"/>
     </row>
-    <row r="93" spans="8:8">
+    <row r="93" spans="1:19">
       <c r="A93" s="19"/>
       <c r="B93" s="19"/>
       <c r="C93" s="19"/>
@@ -3933,7 +3936,7 @@
       <c r="R93" s="19"/>
       <c r="S93" s="19"/>
     </row>
-    <row r="94" spans="8:8">
+    <row r="94" spans="1:19">
       <c r="A94" s="19"/>
       <c r="B94" s="19"/>
       <c r="C94" s="19"/>
@@ -3954,7 +3957,7 @@
       <c r="R94" s="19"/>
       <c r="S94" s="19"/>
     </row>
-    <row r="95" spans="8:8">
+    <row r="95" spans="1:19">
       <c r="A95" s="19"/>
       <c r="B95" s="19"/>
       <c r="C95" s="19"/>
@@ -3975,7 +3978,7 @@
       <c r="R95" s="19"/>
       <c r="S95" s="19"/>
     </row>
-    <row r="96" spans="8:8">
+    <row r="96" spans="1:19">
       <c r="A96" s="19"/>
       <c r="B96" s="19"/>
       <c r="C96" s="19"/>
@@ -3996,7 +3999,7 @@
       <c r="R96" s="19"/>
       <c r="S96" s="19"/>
     </row>
-    <row r="97" spans="8:8">
+    <row r="97" spans="1:19">
       <c r="A97" s="19"/>
       <c r="B97" s="19"/>
       <c r="C97" s="19"/>
@@ -4017,7 +4020,7 @@
       <c r="R97" s="19"/>
       <c r="S97" s="19"/>
     </row>
-    <row r="98" spans="8:8">
+    <row r="98" spans="1:19">
       <c r="A98" s="19"/>
       <c r="B98" s="19"/>
       <c r="C98" s="19"/>
@@ -4038,7 +4041,7 @@
       <c r="R98" s="19"/>
       <c r="S98" s="19"/>
     </row>
-    <row r="99" spans="8:8">
+    <row r="99" spans="1:19">
       <c r="A99" s="19"/>
       <c r="B99" s="19"/>
       <c r="C99" s="19"/>
@@ -4059,7 +4062,7 @@
       <c r="R99" s="19"/>
       <c r="S99" s="19"/>
     </row>
-    <row r="100" spans="8:8">
+    <row r="100" spans="1:19">
       <c r="A100" s="19"/>
       <c r="B100" s="19"/>
       <c r="C100" s="19"/>
@@ -4080,7 +4083,7 @@
       <c r="R100" s="19"/>
       <c r="S100" s="19"/>
     </row>
-    <row r="101" spans="8:8">
+    <row r="101" spans="1:19">
       <c r="A101" s="19"/>
       <c r="B101" s="19"/>
       <c r="C101" s="19"/>
@@ -4101,7 +4104,7 @@
       <c r="R101" s="19"/>
       <c r="S101" s="19"/>
     </row>
-    <row r="102" spans="8:8">
+    <row r="102" spans="1:19">
       <c r="A102" s="19"/>
       <c r="B102" s="19"/>
       <c r="C102" s="19"/>
@@ -4122,7 +4125,7 @@
       <c r="R102" s="19"/>
       <c r="S102" s="19"/>
     </row>
-    <row r="103" spans="8:8">
+    <row r="103" spans="1:19">
       <c r="A103" s="19"/>
       <c r="B103" s="19"/>
       <c r="C103" s="19"/>
@@ -4143,7 +4146,7 @@
       <c r="R103" s="19"/>
       <c r="S103" s="19"/>
     </row>
-    <row r="104" spans="8:8">
+    <row r="104" spans="1:19">
       <c r="A104" s="19"/>
       <c r="B104" s="19"/>
       <c r="C104" s="19"/>
@@ -4164,7 +4167,7 @@
       <c r="R104" s="19"/>
       <c r="S104" s="19"/>
     </row>
-    <row r="105" spans="8:8">
+    <row r="105" spans="1:19">
       <c r="A105" s="19"/>
       <c r="B105" s="19"/>
       <c r="C105" s="19"/>
@@ -4185,7 +4188,7 @@
       <c r="R105" s="19"/>
       <c r="S105" s="19"/>
     </row>
-    <row r="106" spans="8:8">
+    <row r="106" spans="1:19">
       <c r="A106" s="19"/>
       <c r="B106" s="19"/>
       <c r="C106" s="19"/>
@@ -4206,7 +4209,7 @@
       <c r="R106" s="19"/>
       <c r="S106" s="19"/>
     </row>
-    <row r="107" spans="8:8">
+    <row r="107" spans="1:19">
       <c r="A107" s="19"/>
       <c r="B107" s="19"/>
       <c r="C107" s="19"/>
@@ -4227,7 +4230,7 @@
       <c r="R107" s="19"/>
       <c r="S107" s="19"/>
     </row>
-    <row r="108" spans="8:8">
+    <row r="108" spans="1:19">
       <c r="A108" s="19"/>
       <c r="B108" s="19"/>
       <c r="C108" s="19"/>
@@ -4248,7 +4251,7 @@
       <c r="R108" s="19"/>
       <c r="S108" s="19"/>
     </row>
-    <row r="109" spans="8:8">
+    <row r="109" spans="1:19">
       <c r="A109" s="19"/>
       <c r="B109" s="19"/>
       <c r="C109" s="19"/>
@@ -4269,7 +4272,7 @@
       <c r="R109" s="19"/>
       <c r="S109" s="19"/>
     </row>
-    <row r="110" spans="8:8">
+    <row r="110" spans="1:19">
       <c r="A110" s="19"/>
       <c r="B110" s="19"/>
       <c r="C110" s="19"/>
@@ -4290,7 +4293,7 @@
       <c r="R110" s="19"/>
       <c r="S110" s="19"/>
     </row>
-    <row r="111" spans="8:8">
+    <row r="111" spans="1:19">
       <c r="A111" s="19"/>
       <c r="B111" s="19"/>
       <c r="C111" s="19"/>
@@ -4311,7 +4314,7 @@
       <c r="R111" s="19"/>
       <c r="S111" s="19"/>
     </row>
-    <row r="112" spans="8:8">
+    <row r="112" spans="1:19">
       <c r="A112" s="19"/>
       <c r="B112" s="19"/>
       <c r="C112" s="19"/>
@@ -4332,7 +4335,7 @@
       <c r="R112" s="19"/>
       <c r="S112" s="19"/>
     </row>
-    <row r="113" spans="8:8">
+    <row r="113" spans="1:19">
       <c r="A113" s="19"/>
       <c r="B113" s="19"/>
       <c r="C113" s="19"/>
@@ -4353,7 +4356,7 @@
       <c r="R113" s="19"/>
       <c r="S113" s="19"/>
     </row>
-    <row r="114" spans="8:8">
+    <row r="114" spans="1:19">
       <c r="A114" s="19"/>
       <c r="B114" s="19"/>
       <c r="C114" s="19"/>
@@ -4374,7 +4377,7 @@
       <c r="R114" s="19"/>
       <c r="S114" s="19"/>
     </row>
-    <row r="115" spans="8:8">
+    <row r="115" spans="1:19">
       <c r="A115" s="19"/>
       <c r="B115" s="19"/>
       <c r="C115" s="19"/>
@@ -4395,7 +4398,7 @@
       <c r="R115" s="19"/>
       <c r="S115" s="19"/>
     </row>
-    <row r="116" spans="8:8">
+    <row r="116" spans="1:19">
       <c r="A116" s="19"/>
       <c r="B116" s="19"/>
       <c r="C116" s="19"/>
@@ -4416,7 +4419,7 @@
       <c r="R116" s="19"/>
       <c r="S116" s="19"/>
     </row>
-    <row r="117" spans="8:8">
+    <row r="117" spans="1:19">
       <c r="A117" s="19"/>
       <c r="B117" s="19"/>
       <c r="C117" s="19"/>
@@ -4437,7 +4440,7 @@
       <c r="R117" s="19"/>
       <c r="S117" s="19"/>
     </row>
-    <row r="118" spans="8:8">
+    <row r="118" spans="1:19">
       <c r="A118" s="19"/>
       <c r="B118" s="19"/>
       <c r="C118" s="19"/>
@@ -4458,7 +4461,7 @@
       <c r="R118" s="19"/>
       <c r="S118" s="19"/>
     </row>
-    <row r="119" spans="8:8">
+    <row r="119" spans="1:19">
       <c r="A119" s="19"/>
       <c r="B119" s="19"/>
       <c r="C119" s="19"/>
@@ -4479,7 +4482,7 @@
       <c r="R119" s="19"/>
       <c r="S119" s="19"/>
     </row>
-    <row r="120" spans="8:8">
+    <row r="120" spans="1:19">
       <c r="A120" s="19"/>
       <c r="B120" s="19"/>
       <c r="C120" s="19"/>
@@ -4500,7 +4503,7 @@
       <c r="R120" s="19"/>
       <c r="S120" s="19"/>
     </row>
-    <row r="121" spans="8:8">
+    <row r="121" spans="1:19">
       <c r="A121" s="19"/>
       <c r="B121" s="19"/>
       <c r="C121" s="19"/>
@@ -4521,7 +4524,7 @@
       <c r="R121" s="19"/>
       <c r="S121" s="19"/>
     </row>
-    <row r="122" spans="8:8">
+    <row r="122" spans="1:19">
       <c r="A122" s="19"/>
       <c r="B122" s="19"/>
       <c r="C122" s="19"/>
@@ -4542,7 +4545,7 @@
       <c r="R122" s="19"/>
       <c r="S122" s="19"/>
     </row>
-    <row r="123" spans="8:8">
+    <row r="123" spans="1:19">
       <c r="A123" s="19"/>
       <c r="B123" s="19"/>
       <c r="C123" s="19"/>
@@ -4563,7 +4566,7 @@
       <c r="R123" s="19"/>
       <c r="S123" s="19"/>
     </row>
-    <row r="124" spans="8:8">
+    <row r="124" spans="1:19">
       <c r="A124" s="19"/>
       <c r="B124" s="19"/>
       <c r="C124" s="19"/>
@@ -4584,7 +4587,7 @@
       <c r="R124" s="19"/>
       <c r="S124" s="19"/>
     </row>
-    <row r="125" spans="8:8">
+    <row r="125" spans="1:19">
       <c r="A125" s="19"/>
       <c r="B125" s="19"/>
       <c r="C125" s="19"/>
@@ -4605,7 +4608,7 @@
       <c r="R125" s="19"/>
       <c r="S125" s="19"/>
     </row>
-    <row r="126" spans="8:8">
+    <row r="126" spans="1:19">
       <c r="A126" s="19"/>
       <c r="B126" s="19"/>
       <c r="C126" s="19"/>
@@ -4626,7 +4629,7 @@
       <c r="R126" s="19"/>
       <c r="S126" s="19"/>
     </row>
-    <row r="127" spans="8:8">
+    <row r="127" spans="1:19">
       <c r="A127" s="19"/>
       <c r="B127" s="19"/>
       <c r="C127" s="19"/>
@@ -4647,7 +4650,7 @@
       <c r="R127" s="19"/>
       <c r="S127" s="19"/>
     </row>
-    <row r="128" spans="8:8">
+    <row r="128" spans="1:19">
       <c r="A128" s="19"/>
       <c r="B128" s="19"/>
       <c r="C128" s="19"/>
@@ -4668,7 +4671,7 @@
       <c r="R128" s="19"/>
       <c r="S128" s="19"/>
     </row>
-    <row r="129" spans="8:8">
+    <row r="129" spans="1:19">
       <c r="A129" s="19"/>
       <c r="B129" s="19"/>
       <c r="C129" s="19"/>
@@ -4689,7 +4692,7 @@
       <c r="R129" s="19"/>
       <c r="S129" s="19"/>
     </row>
-    <row r="130" spans="8:8">
+    <row r="130" spans="1:19">
       <c r="A130" s="19"/>
       <c r="B130" s="19"/>
       <c r="C130" s="19"/>
@@ -4710,7 +4713,7 @@
       <c r="R130" s="19"/>
       <c r="S130" s="19"/>
     </row>
-    <row r="131" spans="8:8">
+    <row r="131" spans="1:19">
       <c r="A131" s="19"/>
       <c r="B131" s="19"/>
       <c r="C131" s="19"/>
@@ -4731,7 +4734,7 @@
       <c r="R131" s="19"/>
       <c r="S131" s="19"/>
     </row>
-    <row r="132" spans="8:8">
+    <row r="132" spans="1:19">
       <c r="A132" s="19"/>
       <c r="B132" s="19"/>
       <c r="C132" s="19"/>
@@ -4752,7 +4755,7 @@
       <c r="R132" s="19"/>
       <c r="S132" s="19"/>
     </row>
-    <row r="133" spans="8:8">
+    <row r="133" spans="1:19">
       <c r="A133" s="19"/>
       <c r="B133" s="19"/>
       <c r="C133" s="19"/>
@@ -4773,7 +4776,7 @@
       <c r="R133" s="19"/>
       <c r="S133" s="19"/>
     </row>
-    <row r="134" spans="8:8">
+    <row r="134" spans="1:19">
       <c r="A134" s="19"/>
       <c r="B134" s="19"/>
       <c r="C134" s="19"/>
@@ -4794,7 +4797,7 @@
       <c r="R134" s="19"/>
       <c r="S134" s="19"/>
     </row>
-    <row r="135" spans="8:8">
+    <row r="135" spans="1:19">
       <c r="A135" s="19"/>
       <c r="B135" s="19"/>
       <c r="C135" s="19"/>
@@ -4815,7 +4818,7 @@
       <c r="R135" s="19"/>
       <c r="S135" s="19"/>
     </row>
-    <row r="136" spans="8:8">
+    <row r="136" spans="1:19">
       <c r="A136" s="19"/>
       <c r="B136" s="19"/>
       <c r="C136" s="19"/>
@@ -4836,7 +4839,7 @@
       <c r="R136" s="19"/>
       <c r="S136" s="19"/>
     </row>
-    <row r="137" spans="8:8">
+    <row r="137" spans="1:19">
       <c r="A137" s="19"/>
       <c r="B137" s="19"/>
       <c r="C137" s="19"/>
@@ -4857,7 +4860,7 @@
       <c r="R137" s="19"/>
       <c r="S137" s="19"/>
     </row>
-    <row r="138" spans="8:8">
+    <row r="138" spans="1:19">
       <c r="A138" s="19"/>
       <c r="B138" s="19"/>
       <c r="C138" s="19"/>
@@ -4878,7 +4881,7 @@
       <c r="R138" s="19"/>
       <c r="S138" s="19"/>
     </row>
-    <row r="139" spans="8:8">
+    <row r="139" spans="1:19">
       <c r="A139" s="19"/>
       <c r="B139" s="19"/>
       <c r="C139" s="19"/>
@@ -4899,7 +4902,7 @@
       <c r="R139" s="19"/>
       <c r="S139" s="19"/>
     </row>
-    <row r="140" spans="8:8">
+    <row r="140" spans="1:19">
       <c r="A140" s="19"/>
       <c r="B140" s="19"/>
       <c r="C140" s="19"/>
@@ -4920,7 +4923,7 @@
       <c r="R140" s="19"/>
       <c r="S140" s="19"/>
     </row>
-    <row r="141" spans="8:8">
+    <row r="141" spans="1:19">
       <c r="A141" s="19"/>
       <c r="B141" s="19"/>
       <c r="C141" s="19"/>
@@ -4941,7 +4944,7 @@
       <c r="R141" s="19"/>
       <c r="S141" s="19"/>
     </row>
-    <row r="142" spans="8:8">
+    <row r="142" spans="1:19">
       <c r="A142" s="19"/>
       <c r="B142" s="19"/>
       <c r="C142" s="19"/>
@@ -4962,7 +4965,7 @@
       <c r="R142" s="19"/>
       <c r="S142" s="19"/>
     </row>
-    <row r="143" spans="8:8">
+    <row r="143" spans="1:19">
       <c r="A143" s="19"/>
       <c r="B143" s="19"/>
       <c r="C143" s="19"/>
@@ -4983,7 +4986,7 @@
       <c r="R143" s="19"/>
       <c r="S143" s="19"/>
     </row>
-    <row r="144" spans="8:8">
+    <row r="144" spans="1:19">
       <c r="A144" s="19"/>
       <c r="B144" s="19"/>
       <c r="C144" s="19"/>
@@ -5004,7 +5007,7 @@
       <c r="R144" s="19"/>
       <c r="S144" s="19"/>
     </row>
-    <row r="145" spans="8:8">
+    <row r="145" spans="1:19">
       <c r="A145" s="19"/>
       <c r="B145" s="19"/>
       <c r="C145" s="19"/>
@@ -5025,7 +5028,7 @@
       <c r="R145" s="19"/>
       <c r="S145" s="19"/>
     </row>
-    <row r="146" spans="8:8">
+    <row r="146" spans="1:19">
       <c r="A146" s="19"/>
       <c r="B146" s="19"/>
       <c r="C146" s="19"/>
@@ -5046,7 +5049,7 @@
       <c r="R146" s="19"/>
       <c r="S146" s="19"/>
     </row>
-    <row r="147" spans="8:8">
+    <row r="147" spans="1:19">
       <c r="A147" s="19"/>
       <c r="B147" s="19"/>
       <c r="C147" s="19"/>
@@ -5067,7 +5070,7 @@
       <c r="R147" s="19"/>
       <c r="S147" s="19"/>
     </row>
-    <row r="148" spans="8:8">
+    <row r="148" spans="1:19">
       <c r="A148" s="19"/>
       <c r="B148" s="19"/>
       <c r="C148" s="19"/>
@@ -5088,7 +5091,7 @@
       <c r="R148" s="19"/>
       <c r="S148" s="19"/>
     </row>
-    <row r="149" spans="8:8">
+    <row r="149" spans="1:19">
       <c r="A149" s="19"/>
       <c r="B149" s="19"/>
       <c r="C149" s="19"/>
@@ -5109,7 +5112,7 @@
       <c r="R149" s="19"/>
       <c r="S149" s="19"/>
     </row>
-    <row r="150" spans="8:8">
+    <row r="150" spans="1:19">
       <c r="A150" s="19"/>
       <c r="B150" s="19"/>
       <c r="C150" s="19"/>
@@ -5130,7 +5133,7 @@
       <c r="R150" s="19"/>
       <c r="S150" s="19"/>
     </row>
-    <row r="151" spans="8:8">
+    <row r="151" spans="1:19">
       <c r="A151" s="19"/>
       <c r="B151" s="19"/>
       <c r="C151" s="19"/>
@@ -5151,7 +5154,7 @@
       <c r="R151" s="19"/>
       <c r="S151" s="19"/>
     </row>
-    <row r="152" spans="8:8">
+    <row r="152" spans="1:19">
       <c r="A152" s="19"/>
       <c r="B152" s="19"/>
       <c r="C152" s="19"/>
@@ -5172,7 +5175,7 @@
       <c r="R152" s="19"/>
       <c r="S152" s="19"/>
     </row>
-    <row r="153" spans="8:8">
+    <row r="153" spans="1:19">
       <c r="A153" s="19"/>
       <c r="B153" s="19"/>
       <c r="C153" s="19"/>
@@ -5193,7 +5196,7 @@
       <c r="R153" s="19"/>
       <c r="S153" s="19"/>
     </row>
-    <row r="154" spans="8:8">
+    <row r="154" spans="1:19">
       <c r="A154" s="19"/>
       <c r="B154" s="19"/>
       <c r="C154" s="19"/>
@@ -5214,7 +5217,7 @@
       <c r="R154" s="19"/>
       <c r="S154" s="19"/>
     </row>
-    <row r="155" spans="8:8">
+    <row r="155" spans="1:19">
       <c r="A155" s="19"/>
       <c r="B155" s="19"/>
       <c r="C155" s="19"/>
@@ -5235,7 +5238,7 @@
       <c r="R155" s="19"/>
       <c r="S155" s="19"/>
     </row>
-    <row r="156" spans="8:8">
+    <row r="156" spans="1:19">
       <c r="A156" s="19"/>
       <c r="B156" s="19"/>
       <c r="C156" s="19"/>
@@ -5256,7 +5259,7 @@
       <c r="R156" s="19"/>
       <c r="S156" s="19"/>
     </row>
-    <row r="157" spans="8:8">
+    <row r="157" spans="1:19">
       <c r="A157" s="19"/>
       <c r="B157" s="19"/>
       <c r="C157" s="19"/>
@@ -5277,7 +5280,7 @@
       <c r="R157" s="19"/>
       <c r="S157" s="19"/>
     </row>
-    <row r="158" spans="8:8">
+    <row r="158" spans="1:19">
       <c r="A158" s="19"/>
       <c r="B158" s="19"/>
       <c r="C158" s="19"/>
@@ -5298,7 +5301,7 @@
       <c r="R158" s="19"/>
       <c r="S158" s="19"/>
     </row>
-    <row r="159" spans="8:8">
+    <row r="159" spans="1:19">
       <c r="A159" s="19"/>
       <c r="B159" s="19"/>
       <c r="C159" s="19"/>
@@ -5319,7 +5322,7 @@
       <c r="R159" s="19"/>
       <c r="S159" s="19"/>
     </row>
-    <row r="160" spans="8:8">
+    <row r="160" spans="1:19">
       <c r="A160" s="19"/>
       <c r="B160" s="19"/>
       <c r="C160" s="19"/>
@@ -5340,7 +5343,7 @@
       <c r="R160" s="19"/>
       <c r="S160" s="19"/>
     </row>
-    <row r="161" spans="8:8">
+    <row r="161" spans="1:19">
       <c r="A161" s="19"/>
       <c r="B161" s="19"/>
       <c r="C161" s="19"/>
@@ -5361,7 +5364,7 @@
       <c r="R161" s="19"/>
       <c r="S161" s="19"/>
     </row>
-    <row r="162" spans="8:8">
+    <row r="162" spans="1:19">
       <c r="A162" s="19"/>
       <c r="B162" s="19"/>
       <c r="C162" s="19"/>
@@ -5382,7 +5385,7 @@
       <c r="R162" s="19"/>
       <c r="S162" s="19"/>
     </row>
-    <row r="163" spans="8:8">
+    <row r="163" spans="1:19">
       <c r="A163" s="19"/>
       <c r="B163" s="19"/>
       <c r="C163" s="19"/>
@@ -5403,7 +5406,7 @@
       <c r="R163" s="19"/>
       <c r="S163" s="19"/>
     </row>
-    <row r="164" spans="8:8">
+    <row r="164" spans="1:19">
       <c r="A164" s="19"/>
       <c r="B164" s="19"/>
       <c r="C164" s="19"/>
@@ -5424,7 +5427,7 @@
       <c r="R164" s="19"/>
       <c r="S164" s="19"/>
     </row>
-    <row r="165" spans="8:8">
+    <row r="165" spans="1:19">
       <c r="A165" s="19"/>
       <c r="B165" s="19"/>
       <c r="C165" s="19"/>
@@ -5445,7 +5448,7 @@
       <c r="R165" s="19"/>
       <c r="S165" s="19"/>
     </row>
-    <row r="166" spans="8:8">
+    <row r="166" spans="1:19">
       <c r="A166" s="19"/>
       <c r="B166" s="19"/>
       <c r="C166" s="19"/>
@@ -5466,7 +5469,7 @@
       <c r="R166" s="19"/>
       <c r="S166" s="19"/>
     </row>
-    <row r="167" spans="8:8">
+    <row r="167" spans="1:19">
       <c r="A167" s="19"/>
       <c r="B167" s="19"/>
       <c r="C167" s="19"/>
@@ -5487,7 +5490,7 @@
       <c r="R167" s="19"/>
       <c r="S167" s="19"/>
     </row>
-    <row r="168" spans="8:8">
+    <row r="168" spans="1:19">
       <c r="A168" s="19"/>
       <c r="B168" s="19"/>
       <c r="C168" s="19"/>
@@ -5508,7 +5511,7 @@
       <c r="R168" s="19"/>
       <c r="S168" s="19"/>
     </row>
-    <row r="169" spans="8:8">
+    <row r="169" spans="1:19">
       <c r="A169" s="19"/>
       <c r="B169" s="19"/>
       <c r="C169" s="19"/>
@@ -5529,7 +5532,7 @@
       <c r="R169" s="19"/>
       <c r="S169" s="19"/>
     </row>
-    <row r="170" spans="8:8">
+    <row r="170" spans="1:19">
       <c r="A170" s="19"/>
       <c r="B170" s="19"/>
       <c r="C170" s="19"/>
@@ -5550,7 +5553,7 @@
       <c r="R170" s="19"/>
       <c r="S170" s="19"/>
     </row>
-    <row r="171" spans="8:8">
+    <row r="171" spans="1:19">
       <c r="A171" s="19"/>
       <c r="B171" s="19"/>
       <c r="C171" s="19"/>
@@ -5571,7 +5574,7 @@
       <c r="R171" s="19"/>
       <c r="S171" s="19"/>
     </row>
-    <row r="172" spans="8:8">
+    <row r="172" spans="1:19">
       <c r="A172" s="19"/>
       <c r="B172" s="19"/>
       <c r="C172" s="19"/>
@@ -5592,7 +5595,7 @@
       <c r="R172" s="19"/>
       <c r="S172" s="19"/>
     </row>
-    <row r="173" spans="8:8">
+    <row r="173" spans="1:19">
       <c r="A173" s="19"/>
       <c r="B173" s="19"/>
       <c r="C173" s="19"/>
@@ -5613,7 +5616,7 @@
       <c r="R173" s="19"/>
       <c r="S173" s="19"/>
     </row>
-    <row r="174" spans="8:8">
+    <row r="174" spans="1:19">
       <c r="A174" s="19"/>
       <c r="B174" s="19"/>
       <c r="C174" s="19"/>
@@ -5634,7 +5637,7 @@
       <c r="R174" s="19"/>
       <c r="S174" s="19"/>
     </row>
-    <row r="175" spans="8:8">
+    <row r="175" spans="1:19">
       <c r="A175" s="19"/>
       <c r="B175" s="19"/>
       <c r="C175" s="19"/>
@@ -5655,7 +5658,7 @@
       <c r="R175" s="19"/>
       <c r="S175" s="19"/>
     </row>
-    <row r="176" spans="8:8">
+    <row r="176" spans="1:19">
       <c r="A176" s="19"/>
       <c r="B176" s="19"/>
       <c r="C176" s="19"/>
@@ -5676,7 +5679,7 @@
       <c r="R176" s="19"/>
       <c r="S176" s="19"/>
     </row>
-    <row r="177" spans="8:8">
+    <row r="177" spans="1:19">
       <c r="A177" s="19"/>
       <c r="B177" s="19"/>
       <c r="C177" s="19"/>
@@ -5697,7 +5700,7 @@
       <c r="R177" s="19"/>
       <c r="S177" s="19"/>
     </row>
-    <row r="178" spans="8:8">
+    <row r="178" spans="1:19">
       <c r="A178" s="19"/>
       <c r="B178" s="19"/>
       <c r="C178" s="19"/>
@@ -5718,7 +5721,7 @@
       <c r="R178" s="19"/>
       <c r="S178" s="19"/>
     </row>
-    <row r="179" spans="8:8">
+    <row r="179" spans="1:19">
       <c r="A179" s="19"/>
       <c r="B179" s="19"/>
       <c r="C179" s="19"/>
@@ -5739,7 +5742,7 @@
       <c r="R179" s="19"/>
       <c r="S179" s="19"/>
     </row>
-    <row r="180" spans="8:8">
+    <row r="180" spans="1:19">
       <c r="A180" s="19"/>
       <c r="B180" s="19"/>
       <c r="C180" s="19"/>
@@ -5760,7 +5763,7 @@
       <c r="R180" s="19"/>
       <c r="S180" s="19"/>
     </row>
-    <row r="181" spans="8:8">
+    <row r="181" spans="1:19">
       <c r="A181" s="19"/>
       <c r="B181" s="19"/>
       <c r="C181" s="19"/>
@@ -5781,7 +5784,7 @@
       <c r="R181" s="19"/>
       <c r="S181" s="19"/>
     </row>
-    <row r="182" spans="8:8">
+    <row r="182" spans="1:19">
       <c r="A182" s="19"/>
       <c r="B182" s="19"/>
       <c r="C182" s="19"/>
@@ -5802,7 +5805,7 @@
       <c r="R182" s="19"/>
       <c r="S182" s="19"/>
     </row>
-    <row r="183" spans="8:8">
+    <row r="183" spans="1:19">
       <c r="A183" s="19"/>
       <c r="B183" s="19"/>
       <c r="C183" s="19"/>
@@ -5823,7 +5826,7 @@
       <c r="R183" s="19"/>
       <c r="S183" s="19"/>
     </row>
-    <row r="184" spans="8:8">
+    <row r="184" spans="1:19">
       <c r="A184" s="19"/>
       <c r="B184" s="19"/>
       <c r="C184" s="19"/>
@@ -5844,7 +5847,7 @@
       <c r="R184" s="19"/>
       <c r="S184" s="19"/>
     </row>
-    <row r="185" spans="8:8">
+    <row r="185" spans="1:19">
       <c r="A185" s="19"/>
       <c r="B185" s="19"/>
       <c r="C185" s="19"/>
@@ -5865,7 +5868,7 @@
       <c r="R185" s="19"/>
       <c r="S185" s="19"/>
     </row>
-    <row r="186" spans="8:8">
+    <row r="186" spans="1:19">
       <c r="A186" s="19"/>
       <c r="B186" s="19"/>
       <c r="C186" s="19"/>
@@ -5886,7 +5889,7 @@
       <c r="R186" s="19"/>
       <c r="S186" s="19"/>
     </row>
-    <row r="187" spans="8:8">
+    <row r="187" spans="1:19">
       <c r="A187" s="19"/>
       <c r="B187" s="19"/>
       <c r="C187" s="19"/>
@@ -5907,7 +5910,7 @@
       <c r="R187" s="19"/>
       <c r="S187" s="19"/>
     </row>
-    <row r="188" spans="8:8">
+    <row r="188" spans="1:19">
       <c r="A188" s="19"/>
       <c r="B188" s="19"/>
       <c r="C188" s="19"/>
@@ -5928,7 +5931,7 @@
       <c r="R188" s="19"/>
       <c r="S188" s="19"/>
     </row>
-    <row r="189" spans="8:8">
+    <row r="189" spans="1:19">
       <c r="A189" s="19"/>
       <c r="B189" s="19"/>
       <c r="C189" s="19"/>
@@ -5949,7 +5952,7 @@
       <c r="R189" s="19"/>
       <c r="S189" s="19"/>
     </row>
-    <row r="190" spans="8:8">
+    <row r="190" spans="1:19">
       <c r="A190" s="19"/>
       <c r="B190" s="19"/>
       <c r="C190" s="19"/>
@@ -5970,7 +5973,7 @@
       <c r="R190" s="19"/>
       <c r="S190" s="19"/>
     </row>
-    <row r="191" spans="8:8">
+    <row r="191" spans="1:19">
       <c r="A191" s="19"/>
       <c r="B191" s="19"/>
       <c r="C191" s="19"/>
@@ -5991,7 +5994,7 @@
       <c r="R191" s="19"/>
       <c r="S191" s="19"/>
     </row>
-    <row r="192" spans="8:8">
+    <row r="192" spans="1:19">
       <c r="A192" s="19"/>
       <c r="B192" s="19"/>
       <c r="C192" s="19"/>
@@ -6014,26 +6017,8 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H1">
-    <cfRule type="duplicateValues" priority="24" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>